--- a/cloudflare-deploy/public/library/admin/admin-kr.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-kr.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1835,6 +1835,114 @@
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>느리게로 듣고 또박또박 따라 하면 성조(4성)가 잘 잡혀요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>📢</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>공지 스튜디오 (포스터 + 팝업)</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 알림 센터 → 📢 공지 스튜디오로 들어가요. → ①만들기 탭에서 문구·이미지·동영상으로 포스터를 꾸며요. (크기 조절·서버 저장·재사용 가능) → 완성한 포스터의 ‘📢 팝업으로 게시’ 를 누르면 ②게시·팝업 탭으로 자동 전환돼요. → 게시 탭에서 노출 기간·중단을 설정해 학생 앱 팝업으로 발행해요.</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>이벤트 홍보는 ‘만들기 → 바로 팝업 게시’ 흐름 한 번이면 끝나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>🤖</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>AI 운영비서에게 시키기</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>상단 검색창에 명령을 입력하거나 🎤 마이크로 말해요. → 예: “김민지 강사 스케줄로 가게 해줘” → 주간 스케줄에서 해당 강사를 자동으로 찾아 열어줘요. → 예: “자동 스케줄링 열어줘”, “정산 화면으로” 처럼 메뉴 이동을 시켜요. → AI 응답 카드의 ‘지금 이동 →’ 을 누르면 해당 화면으로 넘어가요.</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>메뉴 이름이 기억나지 않을 땐 하고 싶은 일을 그대로 말해보세요 — 알아서 찾아가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>📔</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>학생 음성 일기 모니터</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 📔 음성 일기(모니터) 카드를 열어요. → 학생 UID 입력 후 조회할 월을 선택하고 ‘조회’ 를 눌러요. → 일기 목록에서 항목을 열면 전사·첨삭·격려·점수를 볼 수 있어요.</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>‘조회가 안 된다’면 대부분 그 학생이 아직 일기를 남기지 않은 경우예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>🤖</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>강사 AI 코칭 검수(운영)</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>관리자 🧲 리텐션 센터 → 💼 강사 코칭 탭으로 들어가요. → 하단 ‘🤖 수업별 AI 코칭(최근)’ 섹션에서 강사별 최근 코칭을 확인해요. → 각 카드의 품질 점수·발화비율·개선점으로 코칭·교육 포인트를 잡아요.</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>품질 점수가 낮게 반복되는 강사는 강사 교육 매뉴얼과 연결해 코칭하세요.</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F229"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4382,44 +4490,583 @@
       <c r="E229" s="33" t="n"/>
       <c r="F229" s="33" t="n"/>
     </row>
+    <row r="231" ht="26" customHeight="1">
+      <c r="A231" s="21" t="inlineStr">
+        <is>
+          <t>22  📢 공지 스튜디오 (포스터 + 팝업)  —  공지·이벤트 포스터를 만들어 학생 앱 팝업으로</t>
+        </is>
+      </c>
+      <c r="B231" s="22" t="n"/>
+      <c r="C231" s="22" t="n"/>
+      <c r="D231" s="22" t="n"/>
+      <c r="E231" s="22" t="n"/>
+      <c r="F231" s="22" t="n"/>
+    </row>
+    <row r="232" ht="42" customHeight="1">
+      <c r="A232" s="23" t="inlineStr">
+        <is>
+          <t>📖 흩어져 있던 ‘포스터 만들기’와 ‘팝업 공지 관리’를 한 곳으로 통합한 기능이에요. ①만들기 탭에서 공지·이벤트 포스터를 디자인하고, 바로 ②게시·팝업 탭으로 넘겨 우리 학원 학생 앱에 팝업으로 띄울 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B232" s="24" t="n"/>
+      <c r="C232" s="24" t="n"/>
+      <c r="D232" s="24" t="n"/>
+      <c r="E232" s="24" t="n"/>
+      <c r="F232" s="24" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B233" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="30" customHeight="1">
+      <c r="A234" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B234" s="28" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 알림 센터 → 📢 공지 스튜디오로 들어가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="30" customHeight="1">
+      <c r="A235" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B235" s="28" t="inlineStr">
+        <is>
+          <t>①만들기 탭에서 문구·이미지·동영상으로 포스터를 꾸며요. (크기 조절·서버 저장·재사용 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="30" customHeight="1">
+      <c r="A236" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B236" s="28" t="inlineStr">
+        <is>
+          <t>완성한 포스터의 ‘📢 팝업으로 게시’ 를 누르면 ②게시·팝업 탭으로 자동 전환돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="30" customHeight="1">
+      <c r="A237" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B237" s="28" t="inlineStr">
+        <is>
+          <t>게시 탭에서 노출 기간·중단을 설정해 학생 앱 팝업으로 발행해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="24" customHeight="1">
+      <c r="A238" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B238" s="30" t="inlineStr">
+        <is>
+          <t>포스터 제작과 팝업 발행이 한 화면 2탭으로 이어져 헷갈리지 않아요.</t>
+        </is>
+      </c>
+      <c r="C238" s="31" t="n"/>
+      <c r="D238" s="31" t="n"/>
+      <c r="E238" s="31" t="n"/>
+      <c r="F238" s="31" t="n"/>
+    </row>
+    <row r="239" ht="24" customHeight="1">
+      <c r="A239" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B239" s="30" t="inlineStr">
+        <is>
+          <t>만든 포스터는 저장해두고 재사용할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C239" s="31" t="n"/>
+      <c r="D239" s="31" t="n"/>
+      <c r="E239" s="31" t="n"/>
+      <c r="F239" s="31" t="n"/>
+    </row>
+    <row r="240" ht="24" customHeight="1">
+      <c r="A240" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B240" s="30" t="inlineStr">
+        <is>
+          <t>AI 비서·사이드바 검색 어느 경로로 들어와도 올바른 탭이 열려요.</t>
+        </is>
+      </c>
+      <c r="C240" s="31" t="n"/>
+      <c r="D240" s="31" t="n"/>
+      <c r="E240" s="31" t="n"/>
+      <c r="F240" s="31" t="n"/>
+    </row>
+    <row r="241" ht="26" customHeight="1">
+      <c r="A241" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 기존 포스터·팝업 데이터는 그대로 유지돼요(통합만 됐고 삭제되지 않았어요).</t>
+        </is>
+      </c>
+      <c r="B241" s="35" t="n"/>
+      <c r="C241" s="35" t="n"/>
+      <c r="D241" s="35" t="n"/>
+      <c r="E241" s="35" t="n"/>
+      <c r="F241" s="35" t="n"/>
+    </row>
+    <row r="242" ht="30" customHeight="1">
+      <c r="A242" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 이벤트 홍보는 ‘만들기 → 바로 팝업 게시’ 흐름 한 번이면 끝나요.</t>
+        </is>
+      </c>
+      <c r="B242" s="33" t="n"/>
+      <c r="C242" s="33" t="n"/>
+      <c r="D242" s="33" t="n"/>
+      <c r="E242" s="33" t="n"/>
+      <c r="F242" s="33" t="n"/>
+    </row>
+    <row r="244" ht="26" customHeight="1">
+      <c r="A244" s="21" t="inlineStr">
+        <is>
+          <t>23  🤖 AI 운영비서에게 시키기  —  “○○ 화면으로 가게 해줘” 한마디로 이동</t>
+        </is>
+      </c>
+      <c r="B244" s="22" t="n"/>
+      <c r="C244" s="22" t="n"/>
+      <c r="D244" s="22" t="n"/>
+      <c r="E244" s="22" t="n"/>
+      <c r="F244" s="22" t="n"/>
+    </row>
+    <row r="245" ht="42" customHeight="1">
+      <c r="A245" s="23" t="inlineStr">
+        <is>
+          <t>📖 상단 통합 검색창(또는 우하단 AI 운영비서) 에 하고 싶은 일을 자연스럽게 말하면, AI가 알아듣고 바로 그 화면으로 이동시켜줘요. 이제 ‘○○ 강사 스케줄로 가게 해줘’, ‘자동 스케줄링 열어줘’ 같은 이동 명령을 정확히 따라요.</t>
+        </is>
+      </c>
+      <c r="B245" s="24" t="n"/>
+      <c r="C245" s="24" t="n"/>
+      <c r="D245" s="24" t="n"/>
+      <c r="E245" s="24" t="n"/>
+      <c r="F245" s="24" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B246" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="30" customHeight="1">
+      <c r="A247" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B247" s="28" t="inlineStr">
+        <is>
+          <t>상단 검색창에 명령을 입력하거나 🎤 마이크로 말해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="30" customHeight="1">
+      <c r="A248" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B248" s="28" t="inlineStr">
+        <is>
+          <t>예: “김민지 강사 스케줄로 가게 해줘” → 주간 스케줄에서 해당 강사를 자동으로 찾아 열어줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="30" customHeight="1">
+      <c r="A249" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B249" s="28" t="inlineStr">
+        <is>
+          <t>예: “자동 스케줄링 열어줘”, “정산 화면으로” 처럼 메뉴 이동을 시켜요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="30" customHeight="1">
+      <c r="A250" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B250" s="28" t="inlineStr">
+        <is>
+          <t>AI 응답 카드의 ‘지금 이동 →’ 을 누르면 해당 화면으로 넘어가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="24" customHeight="1">
+      <c r="A251" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B251" s="30" t="inlineStr">
+        <is>
+          <t>이동 명령은 확실히 이동하고, 설명만 하고 마는 일이 줄었어요.</t>
+        </is>
+      </c>
+      <c r="C251" s="31" t="n"/>
+      <c r="D251" s="31" t="n"/>
+      <c r="E251" s="31" t="n"/>
+      <c r="F251" s="31" t="n"/>
+    </row>
+    <row r="252" ht="24" customHeight="1">
+      <c r="A252" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B252" s="30" t="inlineStr">
+        <is>
+          <t>강사 이름으로 스케줄을 검색하면 검색창 자동 채움 + 필터 + 스크롤까지 돼요.</t>
+        </is>
+      </c>
+      <c r="C252" s="31" t="n"/>
+      <c r="D252" s="31" t="n"/>
+      <c r="E252" s="31" t="n"/>
+      <c r="F252" s="31" t="n"/>
+    </row>
+    <row r="253" ht="24" customHeight="1">
+      <c r="A253" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B253" s="30" t="inlineStr">
+        <is>
+          <t>데이터 조회·통계 질문에는 카드형 답변으로도 도와줘요.</t>
+        </is>
+      </c>
+      <c r="C253" s="31" t="n"/>
+      <c r="D253" s="31" t="n"/>
+      <c r="E253" s="31" t="n"/>
+      <c r="F253" s="31" t="n"/>
+    </row>
+    <row r="254" ht="26" customHeight="1">
+      <c r="A254" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · ‘등록·발송·변경’처럼 실제로 무언가를 바꾸는 명령은 한 번 더 확인해요(안전장치).</t>
+        </is>
+      </c>
+      <c r="B254" s="35" t="n"/>
+      <c r="C254" s="35" t="n"/>
+      <c r="D254" s="35" t="n"/>
+      <c r="E254" s="35" t="n"/>
+      <c r="F254" s="35" t="n"/>
+    </row>
+    <row r="255" ht="30" customHeight="1">
+      <c r="A255" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 메뉴 이름이 기억나지 않을 땐 하고 싶은 일을 그대로 말해보세요 — 알아서 찾아가요.</t>
+        </is>
+      </c>
+      <c r="B255" s="33" t="n"/>
+      <c r="C255" s="33" t="n"/>
+      <c r="D255" s="33" t="n"/>
+      <c r="E255" s="33" t="n"/>
+      <c r="F255" s="33" t="n"/>
+    </row>
+    <row r="257" ht="26" customHeight="1">
+      <c r="A257" s="21" t="inlineStr">
+        <is>
+          <t>24  📔 학생 음성 일기 모니터  —  학생별 영어 일기·AI 첨삭·점수 확인</t>
+        </is>
+      </c>
+      <c r="B257" s="22" t="n"/>
+      <c r="C257" s="22" t="n"/>
+      <c r="D257" s="22" t="n"/>
+      <c r="E257" s="22" t="n"/>
+      <c r="F257" s="22" t="n"/>
+    </row>
+    <row r="258" ht="42" customHeight="1">
+      <c r="A258" s="23" t="inlineStr">
+        <is>
+          <t>📖 학생들이 남긴 AI 음성 일기를 관리자 화면에서 조회할 수 있어요. 학생별로 전사(말한 내용)·AI 첨삭·격려·점수를 월별로 확인해, 꾸준히 쓰는 학생을 격려하고 학습 상태를 파악할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B258" s="24" t="n"/>
+      <c r="C258" s="24" t="n"/>
+      <c r="D258" s="24" t="n"/>
+      <c r="E258" s="24" t="n"/>
+      <c r="F258" s="24" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B259" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="30" customHeight="1">
+      <c r="A260" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B260" s="28" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 📔 음성 일기(모니터) 카드를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="30" customHeight="1">
+      <c r="A261" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B261" s="28" t="inlineStr">
+        <is>
+          <t>학생 UID 입력 후 조회할 월을 선택하고 ‘조회’ 를 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="30" customHeight="1">
+      <c r="A262" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B262" s="28" t="inlineStr">
+        <is>
+          <t>일기 목록에서 항목을 열면 전사·첨삭·격려·점수를 볼 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="24" customHeight="1">
+      <c r="A263" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B263" s="30" t="inlineStr">
+        <is>
+          <t>학생이 실제로 일기를 남겨야 조회돼요(입구는 학생 홈의 📔 카드).</t>
+        </is>
+      </c>
+      <c r="C263" s="31" t="n"/>
+      <c r="D263" s="31" t="n"/>
+      <c r="E263" s="31" t="n"/>
+      <c r="F263" s="31" t="n"/>
+    </row>
+    <row r="264" ht="24" customHeight="1">
+      <c r="A264" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B264" s="30" t="inlineStr">
+        <is>
+          <t>꾸준히 쓰는 학생을 찾아 칭찬·리워드로 연결하면 습관이 굳어져요.</t>
+        </is>
+      </c>
+      <c r="C264" s="31" t="n"/>
+      <c r="D264" s="31" t="n"/>
+      <c r="E264" s="31" t="n"/>
+      <c r="F264" s="31" t="n"/>
+    </row>
+    <row r="265" ht="30" customHeight="1">
+      <c r="A265" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · ‘조회가 안 된다’면 대부분 그 학생이 아직 일기를 남기지 않은 경우예요.</t>
+        </is>
+      </c>
+      <c r="B265" s="33" t="n"/>
+      <c r="C265" s="33" t="n"/>
+      <c r="D265" s="33" t="n"/>
+      <c r="E265" s="33" t="n"/>
+      <c r="F265" s="33" t="n"/>
+    </row>
+    <row r="267" ht="26" customHeight="1">
+      <c r="A267" s="21" t="inlineStr">
+        <is>
+          <t>25  🤖 강사 AI 코칭 검수(운영)  —  수업별 AI 코칭·품질 점수 모아 보기</t>
+        </is>
+      </c>
+      <c r="B267" s="22" t="n"/>
+      <c r="C267" s="22" t="n"/>
+      <c r="D267" s="22" t="n"/>
+      <c r="E267" s="22" t="n"/>
+      <c r="F267" s="22" t="n"/>
+    </row>
+    <row r="268" ht="42" customHeight="1">
+      <c r="A268" s="23" t="inlineStr">
+        <is>
+          <t>📖 수업이 끝날 때마다 AI가 강사에게 남긴 코칭(잘한 점·개선점·수업 품질 점수) 을 관리자 화면에서 최근 순으로 모아 볼 수 있어요. 감시가 아니라 강사 성장 지원·코칭 품질 관리 관점으로 활용하세요.</t>
+        </is>
+      </c>
+      <c r="B268" s="24" t="n"/>
+      <c r="C268" s="24" t="n"/>
+      <c r="D268" s="24" t="n"/>
+      <c r="E268" s="24" t="n"/>
+      <c r="F268" s="24" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B269" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="30" customHeight="1">
+      <c r="A270" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B270" s="28" t="inlineStr">
+        <is>
+          <t>관리자 🧲 리텐션 센터 → 💼 강사 코칭 탭으로 들어가요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="30" customHeight="1">
+      <c r="A271" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B271" s="28" t="inlineStr">
+        <is>
+          <t>하단 ‘🤖 수업별 AI 코칭(최근)’ 섹션에서 강사별 최근 코칭을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="30" customHeight="1">
+      <c r="A272" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B272" s="28" t="inlineStr">
+        <is>
+          <t>각 카드의 품질 점수·발화비율·개선점으로 코칭·교육 포인트를 잡아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="24" customHeight="1">
+      <c r="A273" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B273" s="30" t="inlineStr">
+        <is>
+          <t>전체 강사의 최근 코칭을 한눈에 볼 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C273" s="31" t="n"/>
+      <c r="D273" s="31" t="n"/>
+      <c r="E273" s="31" t="n"/>
+      <c r="F273" s="31" t="n"/>
+    </row>
+    <row r="274" ht="24" customHeight="1">
+      <c r="A274" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B274" s="30" t="inlineStr">
+        <is>
+          <t>관리자에게는 월 누적 요약 중심으로 보여줘 부담이 적어요.</t>
+        </is>
+      </c>
+      <c r="C274" s="31" t="n"/>
+      <c r="D274" s="31" t="n"/>
+      <c r="E274" s="31" t="n"/>
+      <c r="F274" s="31" t="n"/>
+    </row>
+    <row r="275" ht="26" customHeight="1">
+      <c r="A275" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 코칭 문구는 강사 개인 성장용이에요. 평가·징계 목적이 아닌 지원 도구로 쓰는 걸 권장해요.</t>
+        </is>
+      </c>
+      <c r="B275" s="35" t="n"/>
+      <c r="C275" s="35" t="n"/>
+      <c r="D275" s="35" t="n"/>
+      <c r="E275" s="35" t="n"/>
+      <c r="F275" s="35" t="n"/>
+    </row>
+    <row r="276" ht="30" customHeight="1">
+      <c r="A276" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 품질 점수가 낮게 반복되는 강사는 강사 교육 매뉴얼과 연결해 코칭하세요.</t>
+        </is>
+      </c>
+      <c r="B276" s="33" t="n"/>
+      <c r="C276" s="33" t="n"/>
+      <c r="D276" s="33" t="n"/>
+      <c r="E276" s="33" t="n"/>
+      <c r="F276" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="208">
+  <mergeCells count="251">
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B252:F252"/>
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="A189:F189"/>
+    <mergeCell ref="B261:F261"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B184:F184"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B236:F236"/>
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B180:F180"/>
     <mergeCell ref="B223:F223"/>
+    <mergeCell ref="B238:F238"/>
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B253:F253"/>
     <mergeCell ref="A159:F159"/>
     <mergeCell ref="B170:F170"/>
     <mergeCell ref="A200:F200"/>
+    <mergeCell ref="B250:F250"/>
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B53:F53"/>
+    <mergeCell ref="A265:F265"/>
+    <mergeCell ref="B234:F234"/>
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B270:F270"/>
     <mergeCell ref="B174:F174"/>
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B186:F186"/>
+    <mergeCell ref="A258:F258"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="B118:F118"/>
     <mergeCell ref="B143:F143"/>
+    <mergeCell ref="A257:F257"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A60:F60"/>
@@ -4428,15 +5075,18 @@
     <mergeCell ref="B142:F142"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="B213:F213"/>
+    <mergeCell ref="A241:F241"/>
     <mergeCell ref="B160:F160"/>
     <mergeCell ref="A124:F124"/>
     <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B233:F233"/>
     <mergeCell ref="B227:F227"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B72:F72"/>
     <mergeCell ref="B185:F185"/>
     <mergeCell ref="B134:F134"/>
+    <mergeCell ref="A267:F267"/>
     <mergeCell ref="A149:F149"/>
     <mergeCell ref="B121:F121"/>
     <mergeCell ref="A101:F101"/>
@@ -4448,6 +5098,7 @@
     <mergeCell ref="B111:F111"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B98:F98"/>
+    <mergeCell ref="A254:F254"/>
     <mergeCell ref="A135:F135"/>
     <mergeCell ref="B107:F107"/>
     <mergeCell ref="B8:F8"/>
@@ -4465,24 +5116,30 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A176:F176"/>
+    <mergeCell ref="A232:F232"/>
     <mergeCell ref="A114:F114"/>
+    <mergeCell ref="B269:F269"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B239:F239"/>
     <mergeCell ref="B153:F153"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A178:F178"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B251:F251"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B204:F204"/>
     <mergeCell ref="B216:F216"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B271:F271"/>
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="A137:F137"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="B62:F62"/>
+    <mergeCell ref="A268:F268"/>
     <mergeCell ref="A217:F217"/>
     <mergeCell ref="B141:F141"/>
     <mergeCell ref="B193:F193"/>
@@ -4491,19 +5148,28 @@
     <mergeCell ref="B202:F202"/>
     <mergeCell ref="A145:F145"/>
     <mergeCell ref="B215:F215"/>
+    <mergeCell ref="B273:F273"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A210:F210"/>
     <mergeCell ref="A179:F179"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A242:F242"/>
+    <mergeCell ref="B263:F263"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B272:F272"/>
     <mergeCell ref="B161:F161"/>
     <mergeCell ref="A116:F116"/>
+    <mergeCell ref="B259:F259"/>
+    <mergeCell ref="A244:F244"/>
     <mergeCell ref="B181:F181"/>
     <mergeCell ref="B225:F225"/>
+    <mergeCell ref="A231:F231"/>
+    <mergeCell ref="B274:F274"/>
     <mergeCell ref="B191:F191"/>
     <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B249:F249"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="A68:F68"/>
@@ -4512,6 +5178,9 @@
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A83:F83"/>
     <mergeCell ref="B226:F226"/>
+    <mergeCell ref="A245:F245"/>
+    <mergeCell ref="A276:F276"/>
+    <mergeCell ref="B260:F260"/>
     <mergeCell ref="A166:F166"/>
     <mergeCell ref="B183:F183"/>
     <mergeCell ref="B65:F65"/>
@@ -4540,6 +5209,7 @@
     <mergeCell ref="B221:F221"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="B100:F100"/>
+    <mergeCell ref="A255:F255"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="B165:F165"/>
@@ -4548,16 +5218,22 @@
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B140:F140"/>
     <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B264:F264"/>
     <mergeCell ref="A104:F104"/>
+    <mergeCell ref="B247:F247"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="B248:F248"/>
+    <mergeCell ref="B262:F262"/>
     <mergeCell ref="A219:F219"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="B151:F151"/>
+    <mergeCell ref="B235:F235"/>
+    <mergeCell ref="B240:F240"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="A4:F4"/>
@@ -4574,9 +5250,11 @@
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B205:F205"/>
     <mergeCell ref="A220:F220"/>
+    <mergeCell ref="B246:F246"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A148:F148"/>
     <mergeCell ref="B211:F211"/>
+    <mergeCell ref="A275:F275"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B95:F95"/>
@@ -4592,6 +5270,7 @@
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="A25:F25"/>
+    <mergeCell ref="B237:F237"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloudflare-deploy/public/library/admin/admin-kr.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-kr.xlsx
@@ -1130,7 +1130,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>🌐 test.mangoi.co.kr    📞 1588-0000    ✉ support@mangoi.co.kr</t>
+          <t>🌐 www.mangoi.co.kr    📞 1644-0561    ✉ support@mangoi.co.kr</t>
         </is>
       </c>
     </row>

--- a/cloudflare-deploy/public/library/admin/admin-kr.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-kr.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1943,6 +1943,141 @@
       <c r="E28" s="15" t="inlineStr">
         <is>
           <t>품질 점수가 낮게 반복되는 강사는 강사 교육 매뉴얼과 연결해 코칭하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>📱</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>QR 출결 체크</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 QR 출결 카드를 열고 우리 학원 QR 코드를 생성해요. → QR을 인쇄해 입구·데스크에 붙여요. → 학생이 휴대폰 카메라로 스캔하면 체크인 화면에서 출석이 완료돼요. → 대시보드의 출결 현황에서 오늘 출석·시간을 실시간으로 봐요.</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>등원 시간대에 데스크에 태블릿을 세워두면 줄 서지 않고 스캔할 수 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>📞</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>상담 예약 관리</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 상담 예약 카드를 열어요. → 새 예약으로 이름·연락처·희망 일시를 등록하거나, 접수된 예약을 확인해요. → 상담을 마치면 상태를 완료로 바꾸고 메모를 남겨요. → 상담 → 레벨테스트 → 등록으로 자연스럽게 이어가세요.</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>상담 다음 날 안부 연락 한 번이 등록 전환율을 크게 올려줘요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>친구 추천 보상 관리</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 추천 보상 카드를 열어요. → 추천인·피추천인·등록 여부를 목록에서 확인해요. → 조건을 충족한 건은 보상 지급으로 처리해요(포인트·기프티콘 등).</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>신학기 전 ‘친구 추천 이벤트’와 함께 쓰면 등록 문의가 눈에 띄게 늘어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>🗓️</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>연기·변경 요청 승인 처리</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 수업 연기/변경 요청 카드를 열어요. → 대기 중 요청의 강사·수업·사유를 확인해요. → 승인 또는 반려를 누르면 결과가 스케줄과 강사에게 반영돼요.</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>매일 아침 대기 요청을 비우는 습관을 들이면 당일 혼선이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>💬</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>자료실 카카오톡 링크 공유</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>관리자 자료실에서 공유할 파일 옆 💬 카톡 링크복사를 눌러요. → 카카오톡 대화방에 붙여넣기로 보내요. → 받는 사람은 링크를 눌러 원본 화질로 바로 보거나 내려받아요.</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>학부모 단체방에는 영상 설명서 링크 하나면 안내가 끝나요.</t>
         </is>
       </c>
     </row>
@@ -1960,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5018,8 +5153,602 @@
       <c r="E276" s="33" t="n"/>
       <c r="F276" s="33" t="n"/>
     </row>
+    <row r="278" ht="26" customHeight="1">
+      <c r="A278" s="21" t="inlineStr">
+        <is>
+          <t>26  📱 QR 출결 체크  —  QR 한 번 스캔으로 출석 완료</t>
+        </is>
+      </c>
+      <c r="B278" s="22" t="n"/>
+      <c r="C278" s="22" t="n"/>
+      <c r="D278" s="22" t="n"/>
+      <c r="E278" s="22" t="n"/>
+      <c r="F278" s="22" t="n"/>
+    </row>
+    <row r="279" ht="42" customHeight="1">
+      <c r="A279" s="23" t="inlineStr">
+        <is>
+          <t>📖 학원 입구에 출결용 QR 코드를 붙여두면, 학생이 휴대폰으로 스캔하는 순간 출석이 자동 기록돼요. 관리자 대시보드에서 오늘의 출결 현황을 실시간으로 확인할 수 있어 수기 출석부가 필요 없어요.</t>
+        </is>
+      </c>
+      <c r="B279" s="24" t="n"/>
+      <c r="C279" s="24" t="n"/>
+      <c r="D279" s="24" t="n"/>
+      <c r="E279" s="24" t="n"/>
+      <c r="F279" s="24" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B280" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="30" customHeight="1">
+      <c r="A281" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B281" s="28" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 QR 출결 카드를 열고 우리 학원 QR 코드를 생성해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="30" customHeight="1">
+      <c r="A282" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B282" s="28" t="inlineStr">
+        <is>
+          <t>QR을 인쇄해 입구·데스크에 붙여요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="30" customHeight="1">
+      <c r="A283" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B283" s="28" t="inlineStr">
+        <is>
+          <t>학생이 휴대폰 카메라로 스캔하면 체크인 화면에서 출석이 완료돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="30" customHeight="1">
+      <c r="A284" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B284" s="28" t="inlineStr">
+        <is>
+          <t>대시보드의 출결 현황에서 오늘 출석·시간을 실시간으로 봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="24" customHeight="1">
+      <c r="A285" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B285" s="30" t="inlineStr">
+        <is>
+          <t>출석 시각이 자동 기록돼 정확하고 빨라요.</t>
+        </is>
+      </c>
+      <c r="C285" s="31" t="n"/>
+      <c r="D285" s="31" t="n"/>
+      <c r="E285" s="31" t="n"/>
+      <c r="F285" s="31" t="n"/>
+    </row>
+    <row r="286" ht="24" customHeight="1">
+      <c r="A286" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B286" s="30" t="inlineStr">
+        <is>
+          <t>출결 데이터는 학생 관리·리포트와 자동으로 이어져요.</t>
+        </is>
+      </c>
+      <c r="C286" s="31" t="n"/>
+      <c r="D286" s="31" t="n"/>
+      <c r="E286" s="31" t="n"/>
+      <c r="F286" s="31" t="n"/>
+    </row>
+    <row r="287" ht="26" customHeight="1">
+      <c r="A287" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · QR 코드는 우리 학원 전용이에요. 외부에 공유되지 않게 관리하세요.</t>
+        </is>
+      </c>
+      <c r="B287" s="35" t="n"/>
+      <c r="C287" s="35" t="n"/>
+      <c r="D287" s="35" t="n"/>
+      <c r="E287" s="35" t="n"/>
+      <c r="F287" s="35" t="n"/>
+    </row>
+    <row r="288" ht="30" customHeight="1">
+      <c r="A288" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 등원 시간대에 데스크에 태블릿을 세워두면 줄 서지 않고 스캔할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B288" s="33" t="n"/>
+      <c r="C288" s="33" t="n"/>
+      <c r="D288" s="33" t="n"/>
+      <c r="E288" s="33" t="n"/>
+      <c r="F288" s="33" t="n"/>
+    </row>
+    <row r="290" ht="26" customHeight="1">
+      <c r="A290" s="21" t="inlineStr">
+        <is>
+          <t>27  📞 상담 예약 관리  —  신규 상담 접수부터 일정 관리까지</t>
+        </is>
+      </c>
+      <c r="B290" s="22" t="n"/>
+      <c r="C290" s="22" t="n"/>
+      <c r="D290" s="22" t="n"/>
+      <c r="E290" s="22" t="n"/>
+      <c r="F290" s="22" t="n"/>
+    </row>
+    <row r="291" ht="42" customHeight="1">
+      <c r="A291" s="23" t="inlineStr">
+        <is>
+          <t>📖 학부모·신규 문의자의 상담 예약을 접수하고 한 화면에서 관리할 수 있어요. 예약 목록에서 일정·상태(대기/완료) 를 관리하고, 상담 결과를 등록으로 이어가는 흐름을 만들 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B291" s="24" t="n"/>
+      <c r="C291" s="24" t="n"/>
+      <c r="D291" s="24" t="n"/>
+      <c r="E291" s="24" t="n"/>
+      <c r="F291" s="24" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B292" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="30" customHeight="1">
+      <c r="A293" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B293" s="28" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 상담 예약 카드를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="30" customHeight="1">
+      <c r="A294" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B294" s="28" t="inlineStr">
+        <is>
+          <t>새 예약으로 이름·연락처·희망 일시를 등록하거나, 접수된 예약을 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="30" customHeight="1">
+      <c r="A295" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B295" s="28" t="inlineStr">
+        <is>
+          <t>상담을 마치면 상태를 완료로 바꾸고 메모를 남겨요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="30" customHeight="1">
+      <c r="A296" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B296" s="28" t="inlineStr">
+        <is>
+          <t>상담 → 레벨테스트 → 등록으로 자연스럽게 이어가세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="24" customHeight="1">
+      <c r="A297" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B297" s="30" t="inlineStr">
+        <is>
+          <t>예약이 한 곳에 모여 놓치는 상담이 없어요.</t>
+        </is>
+      </c>
+      <c r="C297" s="31" t="n"/>
+      <c r="D297" s="31" t="n"/>
+      <c r="E297" s="31" t="n"/>
+      <c r="F297" s="31" t="n"/>
+    </row>
+    <row r="298" ht="24" customHeight="1">
+      <c r="A298" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B298" s="30" t="inlineStr">
+        <is>
+          <t>상담 이력이 남아 재문의 대응이 쉬워져요.</t>
+        </is>
+      </c>
+      <c r="C298" s="31" t="n"/>
+      <c r="D298" s="31" t="n"/>
+      <c r="E298" s="31" t="n"/>
+      <c r="F298" s="31" t="n"/>
+    </row>
+    <row r="299" ht="30" customHeight="1">
+      <c r="A299" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 상담 다음 날 안부 연락 한 번이 등록 전환율을 크게 올려줘요.</t>
+        </is>
+      </c>
+      <c r="B299" s="33" t="n"/>
+      <c r="C299" s="33" t="n"/>
+      <c r="D299" s="33" t="n"/>
+      <c r="E299" s="33" t="n"/>
+      <c r="F299" s="33" t="n"/>
+    </row>
+    <row r="301" ht="26" customHeight="1">
+      <c r="A301" s="21" t="inlineStr">
+        <is>
+          <t>28  🎁 친구 추천 보상 관리  —  추천 현황 확인 · 보상 지급</t>
+        </is>
+      </c>
+      <c r="B301" s="22" t="n"/>
+      <c r="C301" s="22" t="n"/>
+      <c r="D301" s="22" t="n"/>
+      <c r="E301" s="22" t="n"/>
+      <c r="F301" s="22" t="n"/>
+    </row>
+    <row r="302" ht="42" customHeight="1">
+      <c r="A302" s="23" t="inlineStr">
+        <is>
+          <t>📖 재원생이 친구를 데려오는 추천(리퍼럴) 현황을 조회하고 보상 지급까지 처리할 수 있어요. 누가 누구를 추천했는지, 보상이 지급됐는지 한 화면에서 관리돼 입소문 마케팅을 체계적으로 운영할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B302" s="24" t="n"/>
+      <c r="C302" s="24" t="n"/>
+      <c r="D302" s="24" t="n"/>
+      <c r="E302" s="24" t="n"/>
+      <c r="F302" s="24" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B303" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="30" customHeight="1">
+      <c r="A304" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B304" s="28" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 추천 보상 카드를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="30" customHeight="1">
+      <c r="A305" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B305" s="28" t="inlineStr">
+        <is>
+          <t>추천인·피추천인·등록 여부를 목록에서 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="30" customHeight="1">
+      <c r="A306" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B306" s="28" t="inlineStr">
+        <is>
+          <t>조건을 충족한 건은 보상 지급으로 처리해요(포인트·기프티콘 등).</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="24" customHeight="1">
+      <c r="A307" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B307" s="30" t="inlineStr">
+        <is>
+          <t>추천 이력이 데이터로 남아 분쟁 없이 투명해요.</t>
+        </is>
+      </c>
+      <c r="C307" s="31" t="n"/>
+      <c r="D307" s="31" t="n"/>
+      <c r="E307" s="31" t="n"/>
+      <c r="F307" s="31" t="n"/>
+    </row>
+    <row r="308" ht="24" customHeight="1">
+      <c r="A308" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B308" s="30" t="inlineStr">
+        <is>
+          <t>보상 정책을 학생 포인트·상점과 연결하면 효과가 커져요.</t>
+        </is>
+      </c>
+      <c r="C308" s="31" t="n"/>
+      <c r="D308" s="31" t="n"/>
+      <c r="E308" s="31" t="n"/>
+      <c r="F308" s="31" t="n"/>
+    </row>
+    <row r="309" ht="30" customHeight="1">
+      <c r="A309" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 신학기 전 ‘친구 추천 이벤트’와 함께 쓰면 등록 문의가 눈에 띄게 늘어요.</t>
+        </is>
+      </c>
+      <c r="B309" s="33" t="n"/>
+      <c r="C309" s="33" t="n"/>
+      <c r="D309" s="33" t="n"/>
+      <c r="E309" s="33" t="n"/>
+      <c r="F309" s="33" t="n"/>
+    </row>
+    <row r="311" ht="26" customHeight="1">
+      <c r="A311" s="21" t="inlineStr">
+        <is>
+          <t>29  🗓️ 연기·변경 요청 승인 처리  —  강사가 제출한 요청을 확인·승인</t>
+        </is>
+      </c>
+      <c r="B311" s="22" t="n"/>
+      <c r="C311" s="22" t="n"/>
+      <c r="D311" s="22" t="n"/>
+      <c r="E311" s="22" t="n"/>
+      <c r="F311" s="22" t="n"/>
+    </row>
+    <row r="312" ht="42" customHeight="1">
+      <c r="A312" s="23" t="inlineStr">
+        <is>
+          <t>📖 강사가 제출한 수업 연기·시간 변경 요청이 관리자 화면에 실시간으로 모여요. 요청 사유를 확인하고 승인/반려하면 스케줄에 바로 반영돼, 전화·메신저로 오가던 일정 조율이 한 화면에서 끝나요.</t>
+        </is>
+      </c>
+      <c r="B312" s="24" t="n"/>
+      <c r="C312" s="24" t="n"/>
+      <c r="D312" s="24" t="n"/>
+      <c r="E312" s="24" t="n"/>
+      <c r="F312" s="24" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B313" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="30" customHeight="1">
+      <c r="A314" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B314" s="28" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 수업 연기/변경 요청 카드를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="30" customHeight="1">
+      <c r="A315" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B315" s="28" t="inlineStr">
+        <is>
+          <t>대기 중 요청의 강사·수업·사유를 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="30" customHeight="1">
+      <c r="A316" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B316" s="28" t="inlineStr">
+        <is>
+          <t>승인 또는 반려를 누르면 결과가 스케줄과 강사에게 반영돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="24" customHeight="1">
+      <c r="A317" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B317" s="30" t="inlineStr">
+        <is>
+          <t>요청·처리 이력이 남아 분쟁 없이 투명해요.</t>
+        </is>
+      </c>
+      <c r="C317" s="31" t="n"/>
+      <c r="D317" s="31" t="n"/>
+      <c r="E317" s="31" t="n"/>
+      <c r="F317" s="31" t="n"/>
+    </row>
+    <row r="318" ht="24" customHeight="1">
+      <c r="A318" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B318" s="30" t="inlineStr">
+        <is>
+          <t>학부모 안내가 필요한 변경은 승인 후 바로 알림으로 이어가세요.</t>
+        </is>
+      </c>
+      <c r="C318" s="31" t="n"/>
+      <c r="D318" s="31" t="n"/>
+      <c r="E318" s="31" t="n"/>
+      <c r="F318" s="31" t="n"/>
+    </row>
+    <row r="319" ht="30" customHeight="1">
+      <c r="A319" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 매일 아침 대기 요청을 비우는 습관을 들이면 당일 혼선이 없어요.</t>
+        </is>
+      </c>
+      <c r="B319" s="33" t="n"/>
+      <c r="C319" s="33" t="n"/>
+      <c r="D319" s="33" t="n"/>
+      <c r="E319" s="33" t="n"/>
+      <c r="F319" s="33" t="n"/>
+    </row>
+    <row r="321" ht="26" customHeight="1">
+      <c r="A321" s="21" t="inlineStr">
+        <is>
+          <t>30  💬 자료실 카카오톡 링크 공유  —  영상·문서를 원본 화질 그대로 카톡으로</t>
+        </is>
+      </c>
+      <c r="B321" s="22" t="n"/>
+      <c r="C321" s="22" t="n"/>
+      <c r="D321" s="22" t="n"/>
+      <c r="E321" s="22" t="n"/>
+      <c r="F321" s="22" t="n"/>
+    </row>
+    <row r="322" ht="42" customHeight="1">
+      <c r="A322" s="23" t="inlineStr">
+        <is>
+          <t>📖 자료실의 설명서·영상마다 ‘💬 카톡 링크복사’ 버튼이 생겼어요. 카카오톡에 파일을 첨부하면 화질이 눌리지만, 링크로 보내면 원본 화질 그대로 재생돼요. 버튼 한 번으로 링크가 복사되니 학부모·강사 안내가 훨씬 쉬워요.</t>
+        </is>
+      </c>
+      <c r="B322" s="24" t="n"/>
+      <c r="C322" s="24" t="n"/>
+      <c r="D322" s="24" t="n"/>
+      <c r="E322" s="24" t="n"/>
+      <c r="F322" s="24" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B323" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="30" customHeight="1">
+      <c r="A324" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B324" s="28" t="inlineStr">
+        <is>
+          <t>관리자 자료실에서 공유할 파일 옆 💬 카톡 링크복사를 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="30" customHeight="1">
+      <c r="A325" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B325" s="28" t="inlineStr">
+        <is>
+          <t>카카오톡 대화방에 붙여넣기로 보내요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="30" customHeight="1">
+      <c r="A326" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B326" s="28" t="inlineStr">
+        <is>
+          <t>받는 사람은 링크를 눌러 원본 화질로 바로 보거나 내려받아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="24" customHeight="1">
+      <c r="A327" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B327" s="30" t="inlineStr">
+        <is>
+          <t>동영상은 링크 공유 = 원본 화질, 파일 첨부는 화질이 떨어져요.</t>
+        </is>
+      </c>
+      <c r="C327" s="31" t="n"/>
+      <c r="D327" s="31" t="n"/>
+      <c r="E327" s="31" t="n"/>
+      <c r="F327" s="31" t="n"/>
+    </row>
+    <row r="328" ht="24" customHeight="1">
+      <c r="A328" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B328" s="30" t="inlineStr">
+        <is>
+          <t>설명서 PDF·PPT·영상 등 자료실 어디서나 같은 방식으로 공유돼요.</t>
+        </is>
+      </c>
+      <c r="C328" s="31" t="n"/>
+      <c r="D328" s="31" t="n"/>
+      <c r="E328" s="31" t="n"/>
+      <c r="F328" s="31" t="n"/>
+    </row>
+    <row r="329" ht="26" customHeight="1">
+      <c r="A329" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 링크를 받은 사람은 누구나 열 수 있어요. 내부용 자료는 공유 대상을 확인하세요.</t>
+        </is>
+      </c>
+      <c r="B329" s="35" t="n"/>
+      <c r="C329" s="35" t="n"/>
+      <c r="D329" s="35" t="n"/>
+      <c r="E329" s="35" t="n"/>
+      <c r="F329" s="35" t="n"/>
+    </row>
+    <row r="330" ht="30" customHeight="1">
+      <c r="A330" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 학부모 단체방에는 영상 설명서 링크 하나면 안내가 끝나요.</t>
+        </is>
+      </c>
+      <c r="B330" s="33" t="n"/>
+      <c r="C330" s="33" t="n"/>
+      <c r="D330" s="33" t="n"/>
+      <c r="E330" s="33" t="n"/>
+      <c r="F330" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="251">
+  <mergeCells count="300">
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B129:F129"/>
@@ -5031,6 +5760,7 @@
     <mergeCell ref="A189:F189"/>
     <mergeCell ref="B261:F261"/>
     <mergeCell ref="A158:F158"/>
+    <mergeCell ref="B292:F292"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B184:F184"/>
     <mergeCell ref="A3:F3"/>
@@ -5039,23 +5769,31 @@
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
+    <mergeCell ref="A301:F301"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B180:F180"/>
     <mergeCell ref="B223:F223"/>
     <mergeCell ref="B238:F238"/>
+    <mergeCell ref="B294:F294"/>
+    <mergeCell ref="B307:F307"/>
+    <mergeCell ref="B303:F303"/>
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B253:F253"/>
+    <mergeCell ref="A321:F321"/>
     <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A290:F290"/>
     <mergeCell ref="B170:F170"/>
     <mergeCell ref="A200:F200"/>
     <mergeCell ref="B250:F250"/>
+    <mergeCell ref="B328:F328"/>
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="A265:F265"/>
     <mergeCell ref="B234:F234"/>
+    <mergeCell ref="A288:F288"/>
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B270:F270"/>
@@ -5063,21 +5801,27 @@
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B186:F186"/>
     <mergeCell ref="A258:F258"/>
+    <mergeCell ref="A329:F329"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="B118:F118"/>
     <mergeCell ref="B143:F143"/>
     <mergeCell ref="A257:F257"/>
     <mergeCell ref="B30:F30"/>
+    <mergeCell ref="A291:F291"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A60:F60"/>
+    <mergeCell ref="B281:F281"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B133:F133"/>
     <mergeCell ref="B142:F142"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="B213:F213"/>
     <mergeCell ref="A241:F241"/>
+    <mergeCell ref="B313:F313"/>
     <mergeCell ref="B160:F160"/>
+    <mergeCell ref="B305:F305"/>
     <mergeCell ref="A124:F124"/>
+    <mergeCell ref="B306:F306"/>
     <mergeCell ref="B144:F144"/>
     <mergeCell ref="B233:F233"/>
     <mergeCell ref="B227:F227"/>
@@ -5095,13 +5839,17 @@
     <mergeCell ref="B105:F105"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B228:F228"/>
+    <mergeCell ref="A278:F278"/>
     <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B293:F293"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="A254:F254"/>
+    <mergeCell ref="A311:F311"/>
     <mergeCell ref="A135:F135"/>
     <mergeCell ref="B107:F107"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B318:F318"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B175:F175"/>
     <mergeCell ref="B88:F88"/>
@@ -5111,7 +5859,9 @@
     <mergeCell ref="A199:F199"/>
     <mergeCell ref="B171:F171"/>
     <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B308:F308"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B317:F317"/>
     <mergeCell ref="A127:F127"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="A48:F48"/>
@@ -5122,7 +5872,9 @@
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B304:F304"/>
     <mergeCell ref="B239:F239"/>
+    <mergeCell ref="A319:F319"/>
     <mergeCell ref="B153:F153"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A178:F178"/>
@@ -5132,15 +5884,18 @@
     <mergeCell ref="B204:F204"/>
     <mergeCell ref="B216:F216"/>
     <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B296:F296"/>
     <mergeCell ref="B173:F173"/>
     <mergeCell ref="B271:F271"/>
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="A137:F137"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B280:F280"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="A268:F268"/>
     <mergeCell ref="A217:F217"/>
+    <mergeCell ref="A330:F330"/>
     <mergeCell ref="B141:F141"/>
     <mergeCell ref="B193:F193"/>
     <mergeCell ref="B150:F150"/>
@@ -5150,8 +5905,11 @@
     <mergeCell ref="B215:F215"/>
     <mergeCell ref="B273:F273"/>
     <mergeCell ref="A26:F26"/>
+    <mergeCell ref="B282:F282"/>
     <mergeCell ref="A210:F210"/>
+    <mergeCell ref="B295:F295"/>
     <mergeCell ref="A179:F179"/>
+    <mergeCell ref="B325:F325"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A242:F242"/>
@@ -5159,9 +5917,12 @@
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B152:F152"/>
     <mergeCell ref="B272:F272"/>
+    <mergeCell ref="A322:F322"/>
     <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B323:F323"/>
     <mergeCell ref="A116:F116"/>
     <mergeCell ref="B259:F259"/>
+    <mergeCell ref="A309:F309"/>
     <mergeCell ref="A244:F244"/>
     <mergeCell ref="B181:F181"/>
     <mergeCell ref="B225:F225"/>
@@ -5170,6 +5931,7 @@
     <mergeCell ref="B191:F191"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B249:F249"/>
+    <mergeCell ref="A299:F299"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="A68:F68"/>
@@ -5182,10 +5944,12 @@
     <mergeCell ref="A276:F276"/>
     <mergeCell ref="B260:F260"/>
     <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A279:F279"/>
     <mergeCell ref="B183:F183"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B324:F324"/>
     <mergeCell ref="B201:F201"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="B139:F139"/>
@@ -5197,7 +5961,9 @@
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="B222:F222"/>
     <mergeCell ref="A168:F168"/>
+    <mergeCell ref="B284:F284"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="A287:F287"/>
     <mergeCell ref="B123:F123"/>
     <mergeCell ref="B154:F154"/>
     <mergeCell ref="B212:F212"/>
@@ -5207,8 +5973,10 @@
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B203:F203"/>
     <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B286:F286"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="B100:F100"/>
+    <mergeCell ref="B327:F327"/>
     <mergeCell ref="A255:F255"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
@@ -5219,12 +5987,14 @@
     <mergeCell ref="B140:F140"/>
     <mergeCell ref="B155:F155"/>
     <mergeCell ref="B264:F264"/>
+    <mergeCell ref="B326:F326"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="B247:F247"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="B77:F77"/>
+    <mergeCell ref="A302:F302"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="B248:F248"/>
@@ -5235,6 +6005,8 @@
     <mergeCell ref="B235:F235"/>
     <mergeCell ref="B240:F240"/>
     <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B297:F297"/>
+    <mergeCell ref="A312:F312"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B132:F132"/>
@@ -5249,12 +6021,17 @@
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B205:F205"/>
+    <mergeCell ref="B283:F283"/>
+    <mergeCell ref="B314:F314"/>
     <mergeCell ref="A220:F220"/>
     <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B298:F298"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A148:F148"/>
     <mergeCell ref="B211:F211"/>
     <mergeCell ref="A275:F275"/>
+    <mergeCell ref="B285:F285"/>
+    <mergeCell ref="B316:F316"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B95:F95"/>
@@ -5264,6 +6041,7 @@
     <mergeCell ref="A197:F197"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="A146:F146"/>
+    <mergeCell ref="B315:F315"/>
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="A187:F187"/>

--- a/cloudflare-deploy/public/library/admin/admin-kr.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-kr.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2078,168 @@
       <c r="E33" s="20" t="inlineStr">
         <is>
           <t>학부모 단체방에는 영상 설명서 링크 하나면 안내가 끝나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>💳</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>수강 등록 · 결제 → 수업 자동 생성</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>학생·학부모에게 수강신청 링크를 안내해요. → 학생이 강사 → 수업 옵션(주 횟수·기간·수업 길이) → 요일·시간 순으로 고릅니다. → 시간 확인이 통과돼야 결제 버튼이 열립니다(충돌 시 결제 불가). → 결제가 확정되면 회차가 한꺼번에 생성됩니다. 관리자 화면 수업 목록에서 확인해요. → 본사 단가·할인율은 단가표 화면에서 관리합니다.</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>상담 → 레벨테스트 → 수강신청 링크 전달 순서로 안내하면 등록 전환이 매끄럽습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>👀</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>수업 관찰 (라이브 참관)</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 수업 관찰 (라이브) 카드를 열어요. → 관리자 UID와 강의실 ID를 넣어요. → 참관 사유를 반드시 적어요(예: 신규 강사 멘토링). → 참관 시작을 누르면 수업 화면이 열려요. 끝나면 참관 종료를 누르세요. → 지난 기록은 참관 기록에서 확인합니다.</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>신규 강사는 첫 2주 동안 주 1회 참관 후 코칭하면 수업 품질이 빨리 안정됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="54" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>🧭</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>새로워진 관리자 화면</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>왼쪽 메뉴 맨 위의 ‹ 접기를 눌러요. 메뉴가 아이콘 띠로 줄어들며 본문이 넓어져요. → 다시 펼치려면 같은 자리의 › 버튼을 눌러요. → 접은 상태는 다음 접속 때도 그대로 기억됩니다. → 메뉴가 많아 찾기 어려우면 위쪽 메뉴 검색에 이름을 쳐 보세요.</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>정산·급여처럼 표가 넓은 화면은 접어 놓고 보면 훨씬 편합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="54" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>🌐</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>화면 언어가 자동으로 맞춰져요</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>계정에 국적이 등록돼 있으면 로그인할 때 자동으로 맞는 언어가 뜹니다. → 직접 바꾸려면 상단의 🌐 EN / KR 버튼을 눌러요. → 직접 고른 언어는 그 계정에만 저장돼요 — 같은 PC를 여러 명이 써도 섞이지 않습니다. → 강사용 안내 슬라이드·안내서도 영어판으로 함께 바뀝니다.</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>새 강사를 등록할 때 국적을 함께 입력하면 첫 로그인부터 영어 화면으로 시작해 문의가 줄어듭니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="54" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>판단력 훈련 운영 (학생 판단력 지수)</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>학생 화면의 AI 학습 도구 → 판단력 훈련이 기능 위치입니다. → 학생별 누적 결과는 내 성장 화면과 학습 리포트에서 확인해요. → 상담 때 지수 변화 그래프를 근거 자료로 보여 주세요.</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>“단어는 아는데 말이 안 나와요” 하는 학부모 문의에 가장 잘 맞는 설명 자료입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="54" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>🔑</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>강사 계정 관리 (비밀번호 재설정 · 접근 제한)</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 강사 통합에서 해당 강사를 찾아요. → 비밀번호 재설정으로 임시 비밀번호를 발급해요. → 강사에게 전달하고 로그인 후 바로 변경하도록 안내해요. → 강사 계정의 국적이 비어 있으면 국적을 채워 영어 화면이 뜨게 해요.</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>신규 강사 등록 시 국적·연락처를 함께 채워 두면 이후 문의가 확 줄어듭니다.</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F330"/>
+  <dimension ref="A1:F408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5747,306 +5909,1264 @@
       <c r="E330" s="33" t="n"/>
       <c r="F330" s="33" t="n"/>
     </row>
+    <row r="332" ht="26" customHeight="1">
+      <c r="A332" s="21" t="inlineStr">
+        <is>
+          <t>31  💳 수강 등록 · 결제 → 수업 자동 생성  —  결제 확정되면 회차 전량이 자동으로 잡힙니다</t>
+        </is>
+      </c>
+      <c r="B332" s="22" t="n"/>
+      <c r="C332" s="22" t="n"/>
+      <c r="D332" s="22" t="n"/>
+      <c r="E332" s="22" t="n"/>
+      <c r="F332" s="22" t="n"/>
+    </row>
+    <row r="333" ht="42" customHeight="1">
+      <c r="A333" s="23" t="inlineStr">
+        <is>
+          <t>📖 수강신청 화면에서 학생이 강사·요일·시간을 고르고 결제하면, 결제 확정 시점에 수업 회차가 전량 자동 생성됩니다. 예전처럼 결제 확인 후 사람이 일일이 시간표를 넣던 작업이 사라졌어요. 같은 시간에 이미 잡힌 수업이 있으면 결제 전에 충돌을 감지해 알려 줍니다.</t>
+        </is>
+      </c>
+      <c r="B333" s="24" t="n"/>
+      <c r="C333" s="24" t="n"/>
+      <c r="D333" s="24" t="n"/>
+      <c r="E333" s="24" t="n"/>
+      <c r="F333" s="24" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B334" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="30" customHeight="1">
+      <c r="A335" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B335" s="28" t="inlineStr">
+        <is>
+          <t>학생·학부모에게 수강신청 링크를 안내해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="30" customHeight="1">
+      <c r="A336" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B336" s="28" t="inlineStr">
+        <is>
+          <t>학생이 강사 → 수업 옵션(주 횟수·기간·수업 길이) → 요일·시간 순으로 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="30" customHeight="1">
+      <c r="A337" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B337" s="28" t="inlineStr">
+        <is>
+          <t>시간 확인이 통과돼야 결제 버튼이 열립니다(충돌 시 결제 불가).</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="30" customHeight="1">
+      <c r="A338" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B338" s="28" t="inlineStr">
+        <is>
+          <t>결제가 확정되면 회차가 한꺼번에 생성됩니다. 관리자 화면 수업 목록에서 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="30" customHeight="1">
+      <c r="A339" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B339" s="28" t="inlineStr">
+        <is>
+          <t>본사 단가·할인율은 단가표 화면에서 관리합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="24" customHeight="1">
+      <c r="A340" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B340" s="30" t="inlineStr">
+        <is>
+          <t>멱등 처리돼서 결제 알림이 중복 들어와도 회차가 두 번 생기지 않아요.</t>
+        </is>
+      </c>
+      <c r="C340" s="31" t="n"/>
+      <c r="D340" s="31" t="n"/>
+      <c r="E340" s="31" t="n"/>
+      <c r="F340" s="31" t="n"/>
+    </row>
+    <row r="341" ht="24" customHeight="1">
+      <c r="A341" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B341" s="30" t="inlineStr">
+        <is>
+          <t>공휴일·기존 수업과 겹치면 뒤로 밀어서 회차 수를 채웁니다.</t>
+        </is>
+      </c>
+      <c r="C341" s="31" t="n"/>
+      <c r="D341" s="31" t="n"/>
+      <c r="E341" s="31" t="n"/>
+      <c r="F341" s="31" t="n"/>
+    </row>
+    <row r="342" ht="24" customHeight="1">
+      <c r="A342" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B342" s="30" t="inlineStr">
+        <is>
+          <t>기간 할인(6개월 -5% · 12개월 -10%)이 금액에 자동 반영됩니다.</t>
+        </is>
+      </c>
+      <c r="C342" s="31" t="n"/>
+      <c r="D342" s="31" t="n"/>
+      <c r="E342" s="31" t="n"/>
+      <c r="F342" s="31" t="n"/>
+    </row>
+    <row r="343" ht="26" customHeight="1">
+      <c r="A343" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 현재는 1단계(등록 → 결제 → 회차 자동 생성) 까지 열려 있습니다. 이후 단계는 순차 반영 예정입니다.</t>
+        </is>
+      </c>
+      <c r="B343" s="35" t="n"/>
+      <c r="C343" s="35" t="n"/>
+      <c r="D343" s="35" t="n"/>
+      <c r="E343" s="35" t="n"/>
+      <c r="F343" s="35" t="n"/>
+    </row>
+    <row r="344" ht="30" customHeight="1">
+      <c r="A344" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 상담 → 레벨테스트 → 수강신청 링크 전달 순서로 안내하면 등록 전환이 매끄럽습니다.</t>
+        </is>
+      </c>
+      <c r="B344" s="33" t="n"/>
+      <c r="C344" s="33" t="n"/>
+      <c r="D344" s="33" t="n"/>
+      <c r="E344" s="33" t="n"/>
+      <c r="F344" s="33" t="n"/>
+    </row>
+    <row r="346" ht="26" customHeight="1">
+      <c r="A346" s="21" t="inlineStr">
+        <is>
+          <t>32  👀 수업 관찰 (라이브 참관)  —  진행 중인 수업을 조용히 들여다보기</t>
+        </is>
+      </c>
+      <c r="B346" s="22" t="n"/>
+      <c r="C346" s="22" t="n"/>
+      <c r="D346" s="22" t="n"/>
+      <c r="E346" s="22" t="n"/>
+      <c r="F346" s="22" t="n"/>
+    </row>
+    <row r="347" ht="42" customHeight="1">
+      <c r="A347" s="23" t="inlineStr">
+        <is>
+          <t>📖 진행 중인 수업에 학생·강사가 모르게 조용히 참관할 수 있습니다. 입장 알림이 전혀 가지 않아 수업 흐름을 방해하지 않고, 신규 강사 멘토링·수업 품질 점검·학부모 민원 확인에 씁니다. 모든 참관 기록은 감사 로그에 영구 저장됩니다.</t>
+        </is>
+      </c>
+      <c r="B347" s="24" t="n"/>
+      <c r="C347" s="24" t="n"/>
+      <c r="D347" s="24" t="n"/>
+      <c r="E347" s="24" t="n"/>
+      <c r="F347" s="24" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B348" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="30" customHeight="1">
+      <c r="A349" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B349" s="28" t="inlineStr">
+        <is>
+          <t>관리자 메뉴에서 수업 관찰 (라이브) 카드를 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="30" customHeight="1">
+      <c r="A350" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B350" s="28" t="inlineStr">
+        <is>
+          <t>관리자 UID와 강의실 ID를 넣어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="30" customHeight="1">
+      <c r="A351" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B351" s="28" t="inlineStr">
+        <is>
+          <t>참관 사유를 반드시 적어요(예: 신규 강사 멘토링).</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="30" customHeight="1">
+      <c r="A352" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B352" s="28" t="inlineStr">
+        <is>
+          <t>참관 시작을 누르면 수업 화면이 열려요. 끝나면 참관 종료를 누르세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="30" customHeight="1">
+      <c r="A353" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B353" s="28" t="inlineStr">
+        <is>
+          <t>지난 기록은 참관 기록에서 확인합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="24" customHeight="1">
+      <c r="A354" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B354" s="30" t="inlineStr">
+        <is>
+          <t>참관 중에는 소리·영상이 상대에게 전송되지 않아요.</t>
+        </is>
+      </c>
+      <c r="C354" s="31" t="n"/>
+      <c r="D354" s="31" t="n"/>
+      <c r="E354" s="31" t="n"/>
+      <c r="F354" s="31" t="n"/>
+    </row>
+    <row r="355" ht="24" customHeight="1">
+      <c r="A355" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B355" s="30" t="inlineStr">
+        <is>
+          <t>참관 사유는 필수 — 학생 사생활 보호 정책입니다.</t>
+        </is>
+      </c>
+      <c r="C355" s="31" t="n"/>
+      <c r="D355" s="31" t="n"/>
+      <c r="E355" s="31" t="n"/>
+      <c r="F355" s="31" t="n"/>
+    </row>
+    <row r="356" ht="24" customHeight="1">
+      <c r="A356" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B356" s="30" t="inlineStr">
+        <is>
+          <t>누가·언제·왜 참관했는지 모두 기록됩니다.</t>
+        </is>
+      </c>
+      <c r="C356" s="31" t="n"/>
+      <c r="D356" s="31" t="n"/>
+      <c r="E356" s="31" t="n"/>
+      <c r="F356" s="31" t="n"/>
+    </row>
+    <row r="357" ht="26" customHeight="1">
+      <c r="A357" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 학생 사생활과 직결된 기능입니다. 업무상 필요한 경우에만 사용하고, 사유를 구체적으로 적어 주세요.</t>
+        </is>
+      </c>
+      <c r="B357" s="35" t="n"/>
+      <c r="C357" s="35" t="n"/>
+      <c r="D357" s="35" t="n"/>
+      <c r="E357" s="35" t="n"/>
+      <c r="F357" s="35" t="n"/>
+    </row>
+    <row r="358" ht="30" customHeight="1">
+      <c r="A358" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 신규 강사는 첫 2주 동안 주 1회 참관 후 코칭하면 수업 품질이 빨리 안정됩니다.</t>
+        </is>
+      </c>
+      <c r="B358" s="33" t="n"/>
+      <c r="C358" s="33" t="n"/>
+      <c r="D358" s="33" t="n"/>
+      <c r="E358" s="33" t="n"/>
+      <c r="F358" s="33" t="n"/>
+    </row>
+    <row r="360" ht="26" customHeight="1">
+      <c r="A360" s="21" t="inlineStr">
+        <is>
+          <t>33  🧭 새로워진 관리자 화면  —  사이드바 접기 · 밝은 배경 · 선 아이콘</t>
+        </is>
+      </c>
+      <c r="B360" s="22" t="n"/>
+      <c r="C360" s="22" t="n"/>
+      <c r="D360" s="22" t="n"/>
+      <c r="E360" s="22" t="n"/>
+      <c r="F360" s="22" t="n"/>
+    </row>
+    <row r="361" ht="42" customHeight="1">
+      <c r="A361" s="23" t="inlineStr">
+        <is>
+          <t>📖 관리자 화면이 눈이 편하고 넓게 바뀌었습니다. 왼쪽 메뉴는 ‹ 접기 버튼으로 아이콘만 남는 좁은 띠(레일) 로 접히고, 배경은 밝은 톤으로 통일됐어요. 메뉴 아이콘도 선(라인) 아이콘으로 정리해 글자가 잘 읽힙니다.</t>
+        </is>
+      </c>
+      <c r="B361" s="24" t="n"/>
+      <c r="C361" s="24" t="n"/>
+      <c r="D361" s="24" t="n"/>
+      <c r="E361" s="24" t="n"/>
+      <c r="F361" s="24" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B362" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="30" customHeight="1">
+      <c r="A363" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B363" s="28" t="inlineStr">
+        <is>
+          <t>왼쪽 메뉴 맨 위의 ‹ 접기를 눌러요. 메뉴가 아이콘 띠로 줄어들며 본문이 넓어져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="30" customHeight="1">
+      <c r="A364" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B364" s="28" t="inlineStr">
+        <is>
+          <t>다시 펼치려면 같은 자리의 › 버튼을 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="30" customHeight="1">
+      <c r="A365" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B365" s="28" t="inlineStr">
+        <is>
+          <t>접은 상태는 다음 접속 때도 그대로 기억됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="30" customHeight="1">
+      <c r="A366" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B366" s="28" t="inlineStr">
+        <is>
+          <t>메뉴가 많아 찾기 어려우면 위쪽 메뉴 검색에 이름을 쳐 보세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="24" customHeight="1">
+      <c r="A367" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B367" s="30" t="inlineStr">
+        <is>
+          <t>표·목록이 많은 화면에서 가로 공간이 크게 늘어나요.</t>
+        </is>
+      </c>
+      <c r="C367" s="31" t="n"/>
+      <c r="D367" s="31" t="n"/>
+      <c r="E367" s="31" t="n"/>
+      <c r="F367" s="31" t="n"/>
+    </row>
+    <row r="368" ht="24" customHeight="1">
+      <c r="A368" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B368" s="30" t="inlineStr">
+        <is>
+          <t>하위 메뉴 15장까지 밝은 테마로 통일돼 화면 간 색 차이가 사라졌어요.</t>
+        </is>
+      </c>
+      <c r="C368" s="31" t="n"/>
+      <c r="D368" s="31" t="n"/>
+      <c r="E368" s="31" t="n"/>
+      <c r="F368" s="31" t="n"/>
+    </row>
+    <row r="369" ht="24" customHeight="1">
+      <c r="A369" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B369" s="30" t="inlineStr">
+        <is>
+          <t>저사양 PC에서도 버벅이지 않도록 접기 애니메이션을 없앴습니다.</t>
+        </is>
+      </c>
+      <c r="C369" s="31" t="n"/>
+      <c r="D369" s="31" t="n"/>
+      <c r="E369" s="31" t="n"/>
+      <c r="F369" s="31" t="n"/>
+    </row>
+    <row r="370" ht="30" customHeight="1">
+      <c r="A370" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 정산·급여처럼 표가 넓은 화면은 접어 놓고 보면 훨씬 편합니다.</t>
+        </is>
+      </c>
+      <c r="B370" s="33" t="n"/>
+      <c r="C370" s="33" t="n"/>
+      <c r="D370" s="33" t="n"/>
+      <c r="E370" s="33" t="n"/>
+      <c r="F370" s="33" t="n"/>
+    </row>
+    <row r="372" ht="26" customHeight="1">
+      <c r="A372" s="21" t="inlineStr">
+        <is>
+          <t>34  🌐 화면 언어가 자동으로 맞춰져요  —  해외 스태프·강사는 영어로 시작</t>
+        </is>
+      </c>
+      <c r="B372" s="22" t="n"/>
+      <c r="C372" s="22" t="n"/>
+      <c r="D372" s="22" t="n"/>
+      <c r="E372" s="22" t="n"/>
+      <c r="F372" s="22" t="n"/>
+    </row>
+    <row r="373" ht="42" customHeight="1">
+      <c r="A373" s="23" t="inlineStr">
+        <is>
+          <t>📖 필리핀 강사와 해외 스태프가 처음부터 영어 화면으로 시작합니다. 계정의 국적 정보를 기준으로 화면 언어가 정해지고, 강사 계정은 이름·이전 선택과 무관하게 항상 영어로 뜹니다. 물론 상단 🌐 EN / KR 버튼으로 언제든 직접 바꿀 수 있어요.</t>
+        </is>
+      </c>
+      <c r="B373" s="24" t="n"/>
+      <c r="C373" s="24" t="n"/>
+      <c r="D373" s="24" t="n"/>
+      <c r="E373" s="24" t="n"/>
+      <c r="F373" s="24" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B374" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="30" customHeight="1">
+      <c r="A375" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B375" s="28" t="inlineStr">
+        <is>
+          <t>계정에 국적이 등록돼 있으면 로그인할 때 자동으로 맞는 언어가 뜹니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="30" customHeight="1">
+      <c r="A376" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B376" s="28" t="inlineStr">
+        <is>
+          <t>직접 바꾸려면 상단의 🌐 EN / KR 버튼을 눌러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="30" customHeight="1">
+      <c r="A377" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B377" s="28" t="inlineStr">
+        <is>
+          <t>직접 고른 언어는 그 계정에만 저장돼요 — 같은 PC를 여러 명이 써도 섞이지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="30" customHeight="1">
+      <c r="A378" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B378" s="28" t="inlineStr">
+        <is>
+          <t>강사용 안내 슬라이드·안내서도 영어판으로 함께 바뀝니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="24" customHeight="1">
+      <c r="A379" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B379" s="30" t="inlineStr">
+        <is>
+          <t>강사 계정은 무조건 영어 — 한국어 화면 때문에 헤매는 일이 없어요.</t>
+        </is>
+      </c>
+      <c r="C379" s="31" t="n"/>
+      <c r="D379" s="31" t="n"/>
+      <c r="E379" s="31" t="n"/>
+      <c r="F379" s="31" t="n"/>
+    </row>
+    <row r="380" ht="24" customHeight="1">
+      <c r="A380" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B380" s="30" t="inlineStr">
+        <is>
+          <t>이름에 붙은 한글 직함 때문에 영문 이름 계정이 한국어로 뜨던 문제도 고쳤어요.</t>
+        </is>
+      </c>
+      <c r="C380" s="31" t="n"/>
+      <c r="D380" s="31" t="n"/>
+      <c r="E380" s="31" t="n"/>
+      <c r="F380" s="31" t="n"/>
+    </row>
+    <row r="381" ht="24" customHeight="1">
+      <c r="A381" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B381" s="30" t="inlineStr">
+        <is>
+          <t>언어 선택이 계정별로 분리돼 해외 계정이 남의 선택에 덮이지 않아요.</t>
+        </is>
+      </c>
+      <c r="C381" s="31" t="n"/>
+      <c r="D381" s="31" t="n"/>
+      <c r="E381" s="31" t="n"/>
+      <c r="F381" s="31" t="n"/>
+    </row>
+    <row r="382" ht="26" customHeight="1">
+      <c r="A382" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 국적이 비어 있는 계정은 기존 방식(이름·아이디 규칙)으로 판단합니다. 강사 등록 시 국적을 꼭 넣어 주세요.</t>
+        </is>
+      </c>
+      <c r="B382" s="35" t="n"/>
+      <c r="C382" s="35" t="n"/>
+      <c r="D382" s="35" t="n"/>
+      <c r="E382" s="35" t="n"/>
+      <c r="F382" s="35" t="n"/>
+    </row>
+    <row r="383" ht="30" customHeight="1">
+      <c r="A383" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 새 강사를 등록할 때 국적을 함께 입력하면 첫 로그인부터 영어 화면으로 시작해 문의가 줄어듭니다.</t>
+        </is>
+      </c>
+      <c r="B383" s="33" t="n"/>
+      <c r="C383" s="33" t="n"/>
+      <c r="D383" s="33" t="n"/>
+      <c r="E383" s="33" t="n"/>
+      <c r="F383" s="33" t="n"/>
+    </row>
+    <row r="385" ht="26" customHeight="1">
+      <c r="A385" s="21" t="inlineStr">
+        <is>
+          <t>35  🧠 판단력 훈련 운영 (학생 판단력 지수)  —  암기가 아니라 판단 — 학습 성과의 새 지표</t>
+        </is>
+      </c>
+      <c r="B385" s="22" t="n"/>
+      <c r="C385" s="22" t="n"/>
+      <c r="D385" s="22" t="n"/>
+      <c r="E385" s="22" t="n"/>
+      <c r="F385" s="22" t="n"/>
+    </row>
+    <row r="386" ht="42" customHeight="1">
+      <c r="A386" s="23" t="inlineStr">
+        <is>
+          <t>📖 판단력 훈련은 학생이 상황에 맞는 표현을 고르고 이유를 설명하는 학습입니다. 결과는 판단력 지수(5개 축)로 쌓여 학부모 상담·리포트에서 “무엇을 외웠나”가 아니라 “얼마나 스스로 판단하나” 를 보여 주는 근거가 됩니다.</t>
+        </is>
+      </c>
+      <c r="B386" s="24" t="n"/>
+      <c r="C386" s="24" t="n"/>
+      <c r="D386" s="24" t="n"/>
+      <c r="E386" s="24" t="n"/>
+      <c r="F386" s="24" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B387" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="30" customHeight="1">
+      <c r="A388" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B388" s="28" t="inlineStr">
+        <is>
+          <t>학생 화면의 AI 학습 도구 → 판단력 훈련이 기능 위치입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="30" customHeight="1">
+      <c r="A389" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B389" s="28" t="inlineStr">
+        <is>
+          <t>학생별 누적 결과는 내 성장 화면과 학습 리포트에서 확인해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="30" customHeight="1">
+      <c r="A390" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B390" s="28" t="inlineStr">
+        <is>
+          <t>상담 때 지수 변화 그래프를 근거 자료로 보여 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="24" customHeight="1">
+      <c r="A391" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B391" s="30" t="inlineStr">
+        <is>
+          <t>최근 답변에 더 큰 가중치(반감기 방식)라 최근 실력이 지수에 빨리 반영돼요.</t>
+        </is>
+      </c>
+      <c r="C391" s="31" t="n"/>
+      <c r="D391" s="31" t="n"/>
+      <c r="E391" s="31" t="n"/>
+      <c r="F391" s="31" t="n"/>
+    </row>
+    <row r="392" ht="24" customHeight="1">
+      <c r="A392" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B392" s="30" t="inlineStr">
+        <is>
+          <t>부분 점수 방식이라 한 번 틀렸다고 지수가 급락하지 않아요.</t>
+        </is>
+      </c>
+      <c r="C392" s="31" t="n"/>
+      <c r="D392" s="31" t="n"/>
+      <c r="E392" s="31" t="n"/>
+      <c r="F392" s="31" t="n"/>
+    </row>
+    <row r="393" ht="24" customHeight="1">
+      <c r="A393" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B393" s="30" t="inlineStr">
+        <is>
+          <t>문제는 주제 24종 × 각도 12종으로 조합돼 학생마다 다른 문제가 나옵니다.</t>
+        </is>
+      </c>
+      <c r="C393" s="31" t="n"/>
+      <c r="D393" s="31" t="n"/>
+      <c r="E393" s="31" t="n"/>
+      <c r="F393" s="31" t="n"/>
+    </row>
+    <row r="394" ht="26" customHeight="1">
+      <c r="A394" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 판단력 지수는 시험 점수가 아니라 성장 추이로 읽어야 정확합니다. 절대값보다 변화 방향을 보세요.</t>
+        </is>
+      </c>
+      <c r="B394" s="35" t="n"/>
+      <c r="C394" s="35" t="n"/>
+      <c r="D394" s="35" t="n"/>
+      <c r="E394" s="35" t="n"/>
+      <c r="F394" s="35" t="n"/>
+    </row>
+    <row r="395" ht="30" customHeight="1">
+      <c r="A395" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · “단어는 아는데 말이 안 나와요” 하는 학부모 문의에 가장 잘 맞는 설명 자료입니다.</t>
+        </is>
+      </c>
+      <c r="B395" s="33" t="n"/>
+      <c r="C395" s="33" t="n"/>
+      <c r="D395" s="33" t="n"/>
+      <c r="E395" s="33" t="n"/>
+      <c r="F395" s="33" t="n"/>
+    </row>
+    <row r="397" ht="26" customHeight="1">
+      <c r="A397" s="21" t="inlineStr">
+        <is>
+          <t>36  🔑 강사 계정 관리 (비밀번호 재설정 · 접근 제한)  —  분실 대응 · 권한 범위 정리</t>
+        </is>
+      </c>
+      <c r="B397" s="22" t="n"/>
+      <c r="C397" s="22" t="n"/>
+      <c r="D397" s="22" t="n"/>
+      <c r="E397" s="22" t="n"/>
+      <c r="F397" s="22" t="n"/>
+    </row>
+    <row r="398" ht="42" customHeight="1">
+      <c r="A398" s="23" t="inlineStr">
+        <is>
+          <t>📖 강사가 비밀번호를 잊었을 때 관리자 화면에서 바로 재설정할 수 있습니다. 또 강사 계정이 접근할 수 있는 범위를 정리해 강사에게 필요 없는 운영·정산 기능은 열리지 않도록 막았습니다.</t>
+        </is>
+      </c>
+      <c r="B398" s="24" t="n"/>
+      <c r="C398" s="24" t="n"/>
+      <c r="D398" s="24" t="n"/>
+      <c r="E398" s="24" t="n"/>
+      <c r="F398" s="24" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B399" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="30" customHeight="1">
+      <c r="A400" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B400" s="28" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 강사 통합에서 해당 강사를 찾아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="30" customHeight="1">
+      <c r="A401" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B401" s="28" t="inlineStr">
+        <is>
+          <t>비밀번호 재설정으로 임시 비밀번호를 발급해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="30" customHeight="1">
+      <c r="A402" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B402" s="28" t="inlineStr">
+        <is>
+          <t>강사에게 전달하고 로그인 후 바로 변경하도록 안내해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="30" customHeight="1">
+      <c r="A403" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B403" s="28" t="inlineStr">
+        <is>
+          <t>강사 계정의 국적이 비어 있으면 국적을 채워 영어 화면이 뜨게 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="24" customHeight="1">
+      <c r="A404" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B404" s="30" t="inlineStr">
+        <is>
+          <t>강사 계정은 운영·정산 기능에 접근할 수 없습니다(32개 영역 차단).</t>
+        </is>
+      </c>
+      <c r="C404" s="31" t="n"/>
+      <c r="D404" s="31" t="n"/>
+      <c r="E404" s="31" t="n"/>
+      <c r="F404" s="31" t="n"/>
+    </row>
+    <row r="405" ht="24" customHeight="1">
+      <c r="A405" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B405" s="30" t="inlineStr">
+        <is>
+          <t>재설정 이력은 기록에 남습니다.</t>
+        </is>
+      </c>
+      <c r="C405" s="31" t="n"/>
+      <c r="D405" s="31" t="n"/>
+      <c r="E405" s="31" t="n"/>
+      <c r="F405" s="31" t="n"/>
+    </row>
+    <row r="406" ht="24" customHeight="1">
+      <c r="A406" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B406" s="30" t="inlineStr">
+        <is>
+          <t>국적이 입력된 강사는 첫 로그인부터 영어 화면으로 시작합니다.</t>
+        </is>
+      </c>
+      <c r="C406" s="31" t="n"/>
+      <c r="D406" s="31" t="n"/>
+      <c r="E406" s="31" t="n"/>
+      <c r="F406" s="31" t="n"/>
+    </row>
+    <row r="407" ht="26" customHeight="1">
+      <c r="A407" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 임시 비밀번호는 카카오톡 등 본인 확인이 되는 경로로만 전달하세요.</t>
+        </is>
+      </c>
+      <c r="B407" s="35" t="n"/>
+      <c r="C407" s="35" t="n"/>
+      <c r="D407" s="35" t="n"/>
+      <c r="E407" s="35" t="n"/>
+      <c r="F407" s="35" t="n"/>
+    </row>
+    <row r="408" ht="30" customHeight="1">
+      <c r="A408" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 신규 강사 등록 시 국적·연락처를 함께 채워 두면 이후 문의가 확 줄어듭니다.</t>
+        </is>
+      </c>
+      <c r="B408" s="33" t="n"/>
+      <c r="C408" s="33" t="n"/>
+      <c r="D408" s="33" t="n"/>
+      <c r="E408" s="33" t="n"/>
+      <c r="F408" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="300">
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="A84:F84"/>
+  <mergeCells count="372">
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B194:F194"/>
-    <mergeCell ref="B252:F252"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="A189:F189"/>
-    <mergeCell ref="B261:F261"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="B292:F292"/>
+    <mergeCell ref="A394:F394"/>
     <mergeCell ref="B122:F122"/>
-    <mergeCell ref="B184:F184"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B236:F236"/>
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="A301:F301"/>
-    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B238:F238"/>
+    <mergeCell ref="B303:F303"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B253:F253"/>
+    <mergeCell ref="B342:F342"/>
+    <mergeCell ref="A372:F372"/>
+    <mergeCell ref="A347:F347"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A257:F257"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B369:F369"/>
+    <mergeCell ref="B356:F356"/>
+    <mergeCell ref="B160:F160"/>
+    <mergeCell ref="B368:F368"/>
+    <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B227:F227"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="A267:F267"/>
+    <mergeCell ref="B228:F228"/>
+    <mergeCell ref="B293:F293"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A333:F333"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="A199:F199"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B317:F317"/>
+    <mergeCell ref="B388:F388"/>
+    <mergeCell ref="B304:F304"/>
+    <mergeCell ref="B375:F375"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="A346:F346"/>
+    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="B141:F141"/>
+    <mergeCell ref="B401:F401"/>
+    <mergeCell ref="B272:F272"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B259:F259"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B274:F274"/>
+    <mergeCell ref="B249:F249"/>
+    <mergeCell ref="B363:F363"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A276:F276"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A207:F207"/>
+    <mergeCell ref="A383:F383"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A370:F370"/>
+    <mergeCell ref="B325:F325"/>
+    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="B390:F390"/>
+    <mergeCell ref="B389:F389"/>
+    <mergeCell ref="B327:F327"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B264:F264"/>
+    <mergeCell ref="B391:F391"/>
+    <mergeCell ref="B247:F247"/>
+    <mergeCell ref="A302:F302"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B262:F262"/>
+    <mergeCell ref="B151:F151"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A156:F156"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="A220:F220"/>
+    <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B211:F211"/>
+    <mergeCell ref="B338:F338"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="B340:F340"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B315:F315"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B404:F404"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="B252:F252"/>
+    <mergeCell ref="B366:F366"/>
     <mergeCell ref="B180:F180"/>
-    <mergeCell ref="B223:F223"/>
-    <mergeCell ref="B238:F238"/>
-    <mergeCell ref="B294:F294"/>
-    <mergeCell ref="B307:F307"/>
-    <mergeCell ref="B303:F303"/>
-    <mergeCell ref="B195:F195"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B253:F253"/>
+    <mergeCell ref="B381:F381"/>
     <mergeCell ref="A321:F321"/>
-    <mergeCell ref="A159:F159"/>
-    <mergeCell ref="A290:F290"/>
+    <mergeCell ref="A386:F386"/>
     <mergeCell ref="B170:F170"/>
-    <mergeCell ref="A200:F200"/>
-    <mergeCell ref="B250:F250"/>
+    <mergeCell ref="A373:F373"/>
     <mergeCell ref="B328:F328"/>
     <mergeCell ref="A81:F81"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="A265:F265"/>
     <mergeCell ref="B234:F234"/>
-    <mergeCell ref="A288:F288"/>
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B270:F270"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B392:F392"/>
     <mergeCell ref="B186:F186"/>
-    <mergeCell ref="A258:F258"/>
-    <mergeCell ref="A329:F329"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="A257:F257"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="A291:F291"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="B281:F281"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B133:F133"/>
-    <mergeCell ref="B142:F142"/>
     <mergeCell ref="A70:F70"/>
-    <mergeCell ref="B213:F213"/>
     <mergeCell ref="A241:F241"/>
-    <mergeCell ref="B313:F313"/>
-    <mergeCell ref="B160:F160"/>
-    <mergeCell ref="B305:F305"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="B306:F306"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B233:F233"/>
-    <mergeCell ref="B227:F227"/>
-    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="A397:F397"/>
     <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B72:F72"/>
     <mergeCell ref="B185:F185"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="A267:F267"/>
-    <mergeCell ref="A149:F149"/>
-    <mergeCell ref="B121:F121"/>
     <mergeCell ref="A101:F101"/>
     <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B96:F96"/>
     <mergeCell ref="B105:F105"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B228:F228"/>
-    <mergeCell ref="A278:F278"/>
-    <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B293:F293"/>
+    <mergeCell ref="B341:F341"/>
     <mergeCell ref="B120:F120"/>
-    <mergeCell ref="B98:F98"/>
     <mergeCell ref="A254:F254"/>
     <mergeCell ref="A311:F311"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B318:F318"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B175:F175"/>
-    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B405:F405"/>
     <mergeCell ref="A125:F125"/>
-    <mergeCell ref="A190:F190"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="A199:F199"/>
     <mergeCell ref="B171:F171"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B308:F308"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B317:F317"/>
     <mergeCell ref="A127:F127"/>
-    <mergeCell ref="B99:F99"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A176:F176"/>
-    <mergeCell ref="A232:F232"/>
     <mergeCell ref="A114:F114"/>
-    <mergeCell ref="B269:F269"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B304:F304"/>
-    <mergeCell ref="B239:F239"/>
-    <mergeCell ref="A319:F319"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="A169:F169"/>
     <mergeCell ref="A178:F178"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B251:F251"/>
-    <mergeCell ref="B76:F76"/>
     <mergeCell ref="B204:F204"/>
-    <mergeCell ref="B216:F216"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B296:F296"/>
     <mergeCell ref="B173:F173"/>
     <mergeCell ref="B271:F271"/>
     <mergeCell ref="B75:F75"/>
-    <mergeCell ref="A137:F137"/>
-    <mergeCell ref="B109:F109"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B280:F280"/>
     <mergeCell ref="B62:F62"/>
-    <mergeCell ref="A268:F268"/>
-    <mergeCell ref="A217:F217"/>
-    <mergeCell ref="A330:F330"/>
-    <mergeCell ref="B141:F141"/>
-    <mergeCell ref="B193:F193"/>
-    <mergeCell ref="B150:F150"/>
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B202:F202"/>
+    <mergeCell ref="B273:F273"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A242:F242"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A244:F244"/>
+    <mergeCell ref="A231:F231"/>
+    <mergeCell ref="A407:F407"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B349:F349"/>
+    <mergeCell ref="A344:F344"/>
+    <mergeCell ref="A229:F229"/>
+    <mergeCell ref="B226:F226"/>
+    <mergeCell ref="A245:F245"/>
+    <mergeCell ref="B364:F364"/>
+    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B284:F284"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="B222:F222"/>
+    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B286:F286"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A255:F255"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="B248:F248"/>
+    <mergeCell ref="A219:F219"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="B235:F235"/>
+    <mergeCell ref="B297:F297"/>
+    <mergeCell ref="B362:F362"/>
+    <mergeCell ref="B337:F337"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B205:F205"/>
+    <mergeCell ref="B339:F339"/>
+    <mergeCell ref="B314:F314"/>
+    <mergeCell ref="B376:F376"/>
+    <mergeCell ref="B403:F403"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="A408:F408"/>
+    <mergeCell ref="A187:F187"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B365:F365"/>
+    <mergeCell ref="B292:F292"/>
+    <mergeCell ref="A189:F189"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B236:F236"/>
+    <mergeCell ref="B307:F307"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="B294:F294"/>
+    <mergeCell ref="B350:F350"/>
+    <mergeCell ref="B195:F195"/>
+    <mergeCell ref="A200:F200"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="A265:F265"/>
+    <mergeCell ref="A357:F357"/>
+    <mergeCell ref="A258:F258"/>
+    <mergeCell ref="A329:F329"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A358:F358"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B313:F313"/>
+    <mergeCell ref="B213:F213"/>
+    <mergeCell ref="B378:F378"/>
+    <mergeCell ref="B305:F305"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A360:F360"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A385:F385"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B318:F318"/>
+    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B308:F308"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A319:F319"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B239:F239"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B374:F374"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="A330:F330"/>
+    <mergeCell ref="A268:F268"/>
+    <mergeCell ref="B150:F150"/>
     <mergeCell ref="A145:F145"/>
     <mergeCell ref="B215:F215"/>
-    <mergeCell ref="B273:F273"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B263:F263"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B323:F323"/>
+    <mergeCell ref="A361:F361"/>
+    <mergeCell ref="B387:F387"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B260:F260"/>
+    <mergeCell ref="A279:F279"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A287:F287"/>
+    <mergeCell ref="A343:F343"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B334:F334"/>
+    <mergeCell ref="B380:F380"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="B165:F165"/>
+    <mergeCell ref="B336:F336"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B400:F400"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B240:F240"/>
+    <mergeCell ref="B402:F402"/>
+    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="B377:F377"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A382:F382"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="A275:F275"/>
+    <mergeCell ref="B316:F316"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B393:F393"/>
+    <mergeCell ref="A146:F146"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B324:F324"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B261:F261"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="B184:F184"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A301:F301"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A290:F290"/>
+    <mergeCell ref="A395:F395"/>
+    <mergeCell ref="B250:F250"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="A332:F332"/>
+    <mergeCell ref="A288:F288"/>
+    <mergeCell ref="B352:F352"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B281:F281"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B355:F355"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B121:F121"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="A278:F278"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B175:F175"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B269:F269"/>
+    <mergeCell ref="A232:F232"/>
+    <mergeCell ref="A169:F169"/>
+    <mergeCell ref="B251:F251"/>
+    <mergeCell ref="B216:F216"/>
+    <mergeCell ref="A398:F398"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="B280:F280"/>
+    <mergeCell ref="B351:F351"/>
+    <mergeCell ref="B193:F193"/>
+    <mergeCell ref="B295:F295"/>
     <mergeCell ref="B282:F282"/>
-    <mergeCell ref="A210:F210"/>
-    <mergeCell ref="B295:F295"/>
     <mergeCell ref="A179:F179"/>
-    <mergeCell ref="B325:F325"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A242:F242"/>
-    <mergeCell ref="B263:F263"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B272:F272"/>
     <mergeCell ref="A322:F322"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B323:F323"/>
     <mergeCell ref="A116:F116"/>
-    <mergeCell ref="B259:F259"/>
     <mergeCell ref="A309:F309"/>
-    <mergeCell ref="A244:F244"/>
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="A231:F231"/>
-    <mergeCell ref="B274:F274"/>
-    <mergeCell ref="B191:F191"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B249:F249"/>
     <mergeCell ref="A299:F299"/>
-    <mergeCell ref="B87:F87"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A117:F117"/>
-    <mergeCell ref="A229:F229"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="A245:F245"/>
-    <mergeCell ref="A276:F276"/>
-    <mergeCell ref="B260:F260"/>
-    <mergeCell ref="A166:F166"/>
-    <mergeCell ref="A279:F279"/>
+    <mergeCell ref="B379:F379"/>
     <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B324:F324"/>
     <mergeCell ref="B201:F201"/>
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="B335:F335"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B164:F164"/>
-    <mergeCell ref="A207:F207"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A103:F103"/>
-    <mergeCell ref="B222:F222"/>
-    <mergeCell ref="A168:F168"/>
-    <mergeCell ref="B284:F284"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="A287:F287"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="B406:F406"/>
     <mergeCell ref="B212:F212"/>
     <mergeCell ref="B206:F206"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B399:F399"/>
     <mergeCell ref="B203:F203"/>
-    <mergeCell ref="B221:F221"/>
-    <mergeCell ref="B286:F286"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="B100:F100"/>
-    <mergeCell ref="B327:F327"/>
-    <mergeCell ref="A255:F255"/>
-    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="B165:F165"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B155:F155"/>
-    <mergeCell ref="B264:F264"/>
     <mergeCell ref="B326:F326"/>
     <mergeCell ref="A104:F104"/>
-    <mergeCell ref="B247:F247"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
     <mergeCell ref="B130:F130"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="A302:F302"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B248:F248"/>
-    <mergeCell ref="B262:F262"/>
-    <mergeCell ref="A219:F219"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="B151:F151"/>
-    <mergeCell ref="B235:F235"/>
-    <mergeCell ref="B240:F240"/>
+    <mergeCell ref="A312:F312"/>
+    <mergeCell ref="B353:F353"/>
     <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B297:F297"/>
-    <mergeCell ref="A312:F312"/>
     <mergeCell ref="B61:F61"/>
-    <mergeCell ref="A4:F4"/>
     <mergeCell ref="B132:F132"/>
-    <mergeCell ref="A209:F209"/>
-    <mergeCell ref="A91:F91"/>
     <mergeCell ref="B119:F119"/>
-    <mergeCell ref="A156:F156"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B38:F38"/>
     <mergeCell ref="B196:F196"/>
-    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B367:F367"/>
     <mergeCell ref="B112:F112"/>
-    <mergeCell ref="B205:F205"/>
     <mergeCell ref="B283:F283"/>
-    <mergeCell ref="B314:F314"/>
-    <mergeCell ref="A220:F220"/>
-    <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B354:F354"/>
+    <mergeCell ref="B348:F348"/>
     <mergeCell ref="B298:F298"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="A148:F148"/>
-    <mergeCell ref="B211:F211"/>
-    <mergeCell ref="A275:F275"/>
     <mergeCell ref="B285:F285"/>
-    <mergeCell ref="B316:F316"/>
-    <mergeCell ref="B55:F55"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B89:F89"/>
     <mergeCell ref="A138:F138"/>
-    <mergeCell ref="A197:F197"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="A146:F146"/>
-    <mergeCell ref="B315:F315"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="A187:F187"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B97:F97"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="B237:F237"/>
   </mergeCells>
